--- a/source.xlsx
+++ b/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\blog\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B987D88C-544F-4838-A129-6FF0C91E796D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15159596-FC5F-45E7-B7F3-0882EF9F10B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4428" yWindow="1380" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4452" yWindow="1524" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -258,7 +258,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -598,7 +598,7 @@
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
     </row>
-    <row r="10" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>2</v>
       </c>

--- a/source.xlsx
+++ b/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\blog\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15159596-FC5F-45E7-B7F3-0882EF9F10B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F021BE7F-C2ED-430C-BAA8-8AD444FE15F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4452" yWindow="1524" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Canada</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -163,6 +163,30 @@
   </si>
   <si>
     <t>Website</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>University of British Columbia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Abbreviation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UBC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Master of Science in Computer Science (MSc)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.grad.ubc.ca/prospective-students/graduate-degree-programs/master-of-science-computer-science</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>For those students contemplating advanced studies in computer science at UBC, completing a master's degree before continuing to the PhD program confers several advantages.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -170,7 +194,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,6 +235,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -247,10 +279,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -259,9 +292,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -539,72 +574,113 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.44140625" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" customWidth="1"/>
+    <col min="1" max="2" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" customWidth="1"/>
+    <col min="8" max="8" width="27.44140625" customWidth="1"/>
+    <col min="9" max="9" width="87.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="6"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="5"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>10</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>11</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="8" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-    </row>
-    <row r="10" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I9" r:id="rId1" xr:uid="{91F1CEDB-55BD-40F7-B5FC-BD9C1BE2F716}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>